--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486774_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486774_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9418</v>
+        <v>4.1764</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1913</v>
+        <v>3.3017</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.8747</v>
       </c>
       <c r="G2" t="n">
         <v>0.7118</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1105</v>
+        <v>0.124</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3866</v>
+        <v>-0.2763</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2761</v>
+        <v>0.4002</v>
       </c>
       <c r="V2" t="n">
         <v>2.3752</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5932</v>
+        <v>1.8787</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1942</v>
+        <v>3.5044</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6009</v>
+        <v>-1.6258</v>
       </c>
       <c r="G3" t="n">
         <v>1.6694</v>
@@ -688,13 +688,13 @@
         <v>1.1585</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5406</v>
+        <v>-0.2552</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6622</v>
+        <v>-0.3519</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1216</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-0.694</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4748</v>
+        <v>-0.2706</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0637</v>
+        <v>1.1189</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5385</v>
+        <v>-1.3895</v>
       </c>
       <c r="G4" t="n">
         <v>1.022</v>
@@ -766,13 +766,13 @@
         <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2593</v>
+        <v>-0.0551</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2207</v>
+        <v>-0.1655</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0386</v>
+        <v>0.1104</v>
       </c>
       <c r="V4" t="n">
         <v>-1.4306</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5688</v>
+        <v>-0.3785</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6153</v>
+        <v>2.7809</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.1842</v>
+        <v>-3.1594</v>
       </c>
       <c r="G5" t="n">
         <v>2.0836</v>
@@ -844,13 +844,13 @@
         <v>0.5792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4248</v>
+        <v>-0.2344</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5518</v>
+        <v>-0.3863</v>
       </c>
       <c r="U5" t="n">
-        <v>0.127</v>
+        <v>0.1519</v>
       </c>
       <c r="V5" t="n">
         <v>-1.8415</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.635</v>
+        <v>-0.5316</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6563</v>
+        <v>-1.5529</v>
       </c>
       <c r="F6" t="n">
         <v>1.0213</v>
@@ -922,10 +922,10 @@
         <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3034</v>
+        <v>-0.2</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5795</v>
+        <v>-0.476</v>
       </c>
       <c r="U6" t="n">
         <v>0.276</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.887</v>
+        <v>-0.5561</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3882</v>
+        <v>-0.8089</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5012</v>
+        <v>0.2529</v>
       </c>
       <c r="G7" t="n">
         <v>-2.7022</v>
@@ -1000,13 +1000,13 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2205</v>
+        <v>0.1104</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9381</v>
+        <v>-0.3589</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7176</v>
+        <v>0.4693</v>
       </c>
       <c r="V7" t="n">
         <v>0.4911</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5972</v>
+        <v>-1.6373</v>
       </c>
       <c r="E8" t="n">
-        <v>0.761</v>
+        <v>0.9196</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.3582</v>
+        <v>-2.5569</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2773</v>
@@ -1078,13 +1078,13 @@
         <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1323</v>
+        <v>-0.1724</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.745</v>
+        <v>-0.5864</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6127</v>
+        <v>0.414</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1876</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5884</v>
+        <v>-3.0732</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5266</v>
+        <v>-0.2498</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0619</v>
+        <v>-2.8235</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5276</v>
+        <v>-0.8786</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8893</v>
+        <v>-1.4211</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3617</v>
+        <v>0.5425</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0735</v>
+        <v>1.9779</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.13</v>
+        <v>0.5107</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2035</v>
+        <v>1.4672</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6011</v>
+        <v>-2.8565</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7593</v>
+        <v>-1.9318</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1582</v>
+        <v>-0.9247</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1931</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0609</v>
+        <v>-0.1724</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6347</v>
+        <v>-0.2969</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6955</v>
+        <v>0.1245</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.3148</v>
+        <v>-1.6361</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.3148</v>
+        <v>-1.6361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6127</v>
+        <v>-3.6285</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3671</v>
+        <v>-1.368</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.2456</v>
+        <v>-2.2605</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8786</v>
+        <v>-0.5276</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4211</v>
+        <v>-0.8893</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5425</v>
+        <v>0.3617</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9779</v>
+        <v>0.0735</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5107</v>
+        <v>-0.13</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4672</v>
+        <v>0.2035</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8565</v>
+        <v>-0.6011</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9318</v>
+        <v>-0.7593</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9247</v>
+        <v>0.1582</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7118</v>
+        <v>0.0208</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4142</v>
+        <v>-0.476</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2977</v>
+        <v>0.4969</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.6361</v>
+        <v>-3.3148</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6361</v>
+        <v>-3.3148</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7925</v>
+        <v>-4.6405</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5764</v>
+        <v>-2.5485</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2161</v>
+        <v>-2.092</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1892</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0753</v>
+        <v>0.2274</v>
       </c>
       <c r="T11" t="n">
-        <v>1.02</v>
+        <v>0.0479</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0554</v>
+        <v>0.1795</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0648</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7191</v>
+        <v>-6.5757</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4198</v>
+        <v>-4.1026</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2992</v>
+        <v>-2.4731</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2588</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.226</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8554</v>
+        <v>-0.5382</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6294</v>
+        <v>0.4555</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5311</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.3405</v>
+        <v>-15.2369</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1089000000000002</v>
+        <v>0.9947999999999988</v>
       </c>
       <c r="F13" t="n">
-        <v>-16.2316</v>
+        <v>-16.2318</v>
       </c>
       <c r="G13" t="n">
         <v>-7.0002</v>
@@ -1468,13 +1468,13 @@
         <v>12.5501</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.793</v>
+        <v>-0.6895</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.9682</v>
+        <v>-3.8645</v>
       </c>
       <c r="U13" t="n">
-        <v>3.175</v>
+        <v>3.1749</v>
       </c>
       <c r="V13" t="n">
         <v>-6.581700000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5301</v>
+        <v>7.2254</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1161</v>
+        <v>4.599</v>
       </c>
       <c r="F14" t="n">
-        <v>2.414</v>
+        <v>2.6264</v>
       </c>
       <c r="G14" t="n">
         <v>6.28</v>
@@ -1546,13 +1546,13 @@
         <v>1.5446</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2081</v>
+        <v>0.9034</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5788</v>
+        <v>0.0616</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6294</v>
+        <v>0.8418</v>
       </c>
       <c r="V14" t="n">
         <v>0.8142</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2735</v>
+        <v>7.1976</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0748</v>
+        <v>6.4885</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1987</v>
+        <v>0.7091</v>
       </c>
       <c r="G15" t="n">
         <v>0.8537</v>
@@ -1624,13 +1624,13 @@
         <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7999000000000001</v>
+        <v>0.1242</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8002</v>
+        <v>-0.3865</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0003</v>
+        <v>0.5107</v>
       </c>
       <c r="V15" t="n">
         <v>4.8681</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.8348</v>
+        <v>5.1629</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7424</v>
+        <v>4.1561</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0924</v>
+        <v>1.0068</v>
       </c>
       <c r="G16" t="n">
         <v>1.2925</v>
@@ -1702,13 +1702,13 @@
         <v>1.9308</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0443</v>
+        <v>0.3724</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0209</v>
+        <v>-0.6072</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0653</v>
+        <v>0.9797</v>
       </c>
       <c r="V16" t="n">
         <v>3.1118</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7855</v>
+        <v>4.3827</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6461</v>
+        <v>2.9564</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1394</v>
+        <v>1.4263</v>
       </c>
       <c r="G17" t="n">
         <v>3.0323</v>
@@ -1780,13 +1780,13 @@
         <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2041</v>
+        <v>0.393</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0209</v>
+        <v>-0.7107</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8168</v>
+        <v>1.1037</v>
       </c>
       <c r="V17" t="n">
         <v>0.5712</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6835</v>
+        <v>1.3276</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2758</v>
+        <v>3.0689</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5923</v>
+        <v>-1.7413</v>
       </c>
       <c r="G18" t="n">
         <v>2.1305</v>
@@ -1858,13 +1858,13 @@
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6455</v>
+        <v>0.2896</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4136</v>
+        <v>0.2067</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2319</v>
+        <v>0.0829</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8995</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3107</v>
+        <v>0.228</v>
       </c>
       <c r="E19" t="n">
-        <v>1.9006</v>
+        <v>1.6937</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5899</v>
+        <v>-1.4657</v>
       </c>
       <c r="G19" t="n">
         <v>0.4708</v>
@@ -1936,13 +1936,13 @@
         <v>1.3515</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1102</v>
+        <v>0.0275</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.2899</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1933</v>
+        <v>0.3174</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6565</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>M. MELERO JAREÑO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.795</v>
+        <v>-0.7919</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6722</v>
+        <v>-0.3748</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8772</v>
+        <v>-0.4171</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2119</v>
+        <v>-1.5505</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2624</v>
+        <v>-0.5241</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9495</v>
+        <v>-1.0264</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1208</v>
+        <v>-0.481</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1234</v>
+        <v>-1.2134</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2442</v>
+        <v>0.7325</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3327</v>
+        <v>-1.0695</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.139</v>
+        <v>0.6893</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1937</v>
+        <v>-1.7588</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.51</v>
+        <v>0.5792</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.4408</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9308</v>
+        <v>0.5792</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6993</v>
+        <v>0.1793</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1925</v>
+        <v>-0.1794</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5068</v>
+        <v>0.3587</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4554</v>
+        <v>0.2856</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MELERO JAREÑO</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0981</v>
+        <v>-1.7287</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5816</v>
+        <v>-2.3961</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5165</v>
+        <v>0.6674</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5505</v>
+        <v>-1.2119</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5241</v>
+        <v>-0.2624</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0264</v>
+        <v>-0.9495</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.481</v>
+        <v>0.1208</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2134</v>
+        <v>-0.1234</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7325</v>
+        <v>0.2442</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0695</v>
+        <v>-1.3327</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6893</v>
+        <v>-0.139</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7588</v>
+        <v>-1.1937</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5792</v>
+        <v>-2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-4.4408</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5792</v>
+        <v>1.9308</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1269</v>
+        <v>0.7655</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3863</v>
+        <v>-0.5315</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2594</v>
+        <v>1.297</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2856</v>
+        <v>2.4554</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2856</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7147</v>
+        <v>-2.7892</v>
       </c>
       <c r="E22" t="n">
         <v>-1.1171</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5976</v>
+        <v>-1.6721</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5379</v>
@@ -2170,13 +2170,13 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0497</v>
+        <v>-0.1242</v>
       </c>
       <c r="T22" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2262</v>
+        <v>0.1518</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5133</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4698</v>
+        <v>-3.1844</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1532</v>
+        <v>-2.843</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3166</v>
+        <v>-0.3414</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7594</v>
@@ -2248,13 +2248,13 @@
         <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7337</v>
+        <v>-0.4483</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7725</v>
+        <v>-0.4623</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0389</v>
+        <v>0.014</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9421</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>16.3405</v>
+        <v>17.03</v>
       </c>
       <c r="E24" t="n">
-        <v>16.2317</v>
+        <v>16.2316</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1088000000000002</v>
+        <v>0.7983999999999998</v>
       </c>
       <c r="G24" t="n">
         <v>7.000100000000002</v>
@@ -2326,13 +2326,13 @@
         <v>13.5154</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7931</v>
+        <v>2.4824</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.1749</v>
+        <v>-3.1751</v>
       </c>
       <c r="U24" t="n">
-        <v>4.9683</v>
+        <v>5.6577</v>
       </c>
       <c r="V24" t="n">
         <v>6.581599999999999</v>
